--- a/sample_data/Sample_Admission.xlsx
+++ b/sample_data/Sample_Admission.xlsx
@@ -425,768 +425,323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Student_ID</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Student_Name</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Applied_Course</t>
+          <t>department_name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Candidate_Category</t>
+          <t>course_name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Class_12_Pct</t>
+          <t>semester</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Entrance_Exam_Score</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Core_Subject_Score</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date_Of_Birth</t>
+          <t>address</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>APP-1001</t>
+          <t>Aarav Roy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Student 1</t>
+          <t>aarav.roy.test2026@university.edu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>B.Tech CSE</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
-      </c>
-      <c r="F2" t="n">
-        <v>90</v>
-      </c>
-      <c r="G2" t="n">
-        <v>95</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9822001101</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>404 Cyber City, Bengaluru, Karnataka</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>APP-1002</t>
+          <t>Pooja Hegde</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Student 2</t>
+          <t>pooja.hegde.test2026@university.edu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OBC</t>
+          <t>B.Tech CSE</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
-      </c>
-      <c r="F3" t="n">
-        <v>97</v>
-      </c>
-      <c r="G3" t="n">
-        <v>94</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9822001102</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12 Brigade Road, Bengaluru, Karnataka</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APP-1003</t>
+          <t>Nikhil Chopra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Student 3</t>
+          <t>nikhil.chopra.test2026@university.edu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>B.Tech IT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
-      </c>
-      <c r="F4" t="n">
-        <v>91</v>
-      </c>
-      <c r="G4" t="n">
-        <v>93</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9822001103</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>77 Connaught Place, New Delhi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APP-1004</t>
+          <t>Anjali Deshmukh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Student 4</t>
+          <t>anjali.deshmukh.test2026@university.edu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>B.Tech IT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>91</v>
-      </c>
-      <c r="F5" t="n">
-        <v>98</v>
-      </c>
-      <c r="G5" t="n">
-        <v>94</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9822001104</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>55 Shivaji Nagar, Pune, Maharashtra</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APP-1005</t>
+          <t>Siddharth Sen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Student 5</t>
+          <t>siddharth.sen.test2026@university.edu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>Computer Applications</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>Master of Computer Applications</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
-      </c>
-      <c r="F6" t="n">
-        <v>94</v>
-      </c>
-      <c r="G6" t="n">
-        <v>95</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9822001105</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>9 Salt Lake Sector V, Kolkata, WB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APP-1006</t>
+          <t>Kavita Pillai</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Student 6</t>
+          <t>kavita.pillai.test2026@university.edu</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>Computer Applications</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>Master of Computer Applications</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
-      </c>
-      <c r="F7" t="n">
-        <v>69</v>
-      </c>
-      <c r="G7" t="n">
-        <v>83</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9822001106</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>18 MG Road, Thiruvananthapuram, Kerala</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APP-1007</t>
+          <t>Varun Grover</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Student 7</t>
+          <t>varun.grover.test2026@university.edu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OBC</t>
+          <t>B.Tech CSE</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
-      </c>
-      <c r="F8" t="n">
-        <v>86</v>
-      </c>
-      <c r="G8" t="n">
-        <v>73</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>9822001107</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>63 Civil Lines, Nagpur, Maharashtra</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APP-1008</t>
+          <t>Sneha Kulkarni</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Student 8</t>
+          <t>sneha.kulkarni.test2026@university.edu</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>B.Tech IT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
-      </c>
-      <c r="F9" t="n">
-        <v>68</v>
-      </c>
-      <c r="G9" t="n">
-        <v>84</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>APP-1009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Student 9</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>EWS</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>84</v>
-      </c>
-      <c r="F10" t="n">
-        <v>72</v>
-      </c>
-      <c r="G10" t="n">
-        <v>62</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>APP-1010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Student 10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>EWS</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>80</v>
-      </c>
-      <c r="F11" t="n">
-        <v>82</v>
-      </c>
-      <c r="G11" t="n">
-        <v>71</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>APP-1011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Student 11</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>OBC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>70</v>
-      </c>
-      <c r="F12" t="n">
-        <v>87</v>
-      </c>
-      <c r="G12" t="n">
-        <v>83</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>APP-1012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Student 12</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>OBC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>82</v>
-      </c>
-      <c r="F13" t="n">
-        <v>70</v>
-      </c>
-      <c r="G13" t="n">
-        <v>76</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>APP-1013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Student 13</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>76</v>
-      </c>
-      <c r="F14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G14" t="n">
-        <v>65</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>APP-1014</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Student 14</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>64</v>
-      </c>
-      <c r="F15" t="n">
-        <v>66</v>
-      </c>
-      <c r="G15" t="n">
-        <v>69</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>APP-1015</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Student 15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>EWS</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>82</v>
-      </c>
-      <c r="F16" t="n">
-        <v>89</v>
-      </c>
-      <c r="G16" t="n">
-        <v>78</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>APP-1016</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Student 16</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>52</v>
-      </c>
-      <c r="F17" t="n">
-        <v>46</v>
-      </c>
-      <c r="G17" t="n">
-        <v>52</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>APP-1017</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Student 17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>OBC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>45</v>
-      </c>
-      <c r="F18" t="n">
-        <v>47</v>
-      </c>
-      <c r="G18" t="n">
-        <v>41</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>APP-1018</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Student 18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>43</v>
-      </c>
-      <c r="F19" t="n">
-        <v>52</v>
-      </c>
-      <c r="G19" t="n">
-        <v>51</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>APP-1019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Student 19</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>EWS</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>40</v>
-      </c>
-      <c r="F20" t="n">
-        <v>52</v>
-      </c>
-      <c r="G20" t="n">
-        <v>40</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>APP-1020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Student 20</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>55</v>
-      </c>
-      <c r="F21" t="n">
-        <v>44</v>
-      </c>
-      <c r="G21" t="n">
-        <v>45</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2000-05-15</t>
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9822001108</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>21 Law College Road, Pune, Maharashtra</t>
         </is>
       </c>
     </row>
